--- a/BerichteGenerierenJSt_2026/data.xlsx
+++ b/BerichteGenerierenJSt_2026/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8c5f5e60cbc7cb48/BerichteGenerierenJSt/BerichteGenerierenJSt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8c5f5e60cbc7cb48/BerichteGenerierenJSt/BerichteGenerierenJSt_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{615000B2-D201-42A9-9881-0A8EEB2B7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A287D147-E368-473A-BA5B-DD22CF0AE053}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{615000B2-D201-42A9-9881-0A8EEB2B7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C53D807A-9F61-4C35-9986-51BB02D62CD8}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="49">
   <si>
     <t>Bericht</t>
   </si>
@@ -66,9 +77,6 @@
     <t>Anwendungsentwickler</t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
     <t>9.2;10.3;</t>
   </si>
   <si>
@@ -78,66 +86,12 @@
     <t xml:space="preserve">Fach </t>
   </si>
   <si>
-    <t>test3</t>
-  </si>
-  <si>
     <t>9.2;10.3</t>
   </si>
   <si>
     <t>9.2;10.7</t>
   </si>
   <si>
-    <t>test9</t>
-  </si>
-  <si>
-    <t>test10</t>
-  </si>
-  <si>
-    <t>test11</t>
-  </si>
-  <si>
-    <t>test12</t>
-  </si>
-  <si>
-    <t>test13</t>
-  </si>
-  <si>
-    <t>test14</t>
-  </si>
-  <si>
-    <t>test15</t>
-  </si>
-  <si>
-    <t>test16</t>
-  </si>
-  <si>
-    <t>test17</t>
-  </si>
-  <si>
-    <t>test18</t>
-  </si>
-  <si>
-    <t>test19</t>
-  </si>
-  <si>
-    <t>test20</t>
-  </si>
-  <si>
-    <t>test21</t>
-  </si>
-  <si>
-    <t>test22</t>
-  </si>
-  <si>
-    <t>test23</t>
-  </si>
-  <si>
-    <t>test24</t>
-  </si>
-  <si>
-    <t>test25</t>
-  </si>
-  <si>
     <t xml:space="preserve">Urlaub </t>
   </si>
   <si>
@@ -147,18 +101,6 @@
     <t xml:space="preserve">Einstieg in Kivy Übungsaufgaben. </t>
   </si>
   <si>
-    <t>Projekt Kivy App erstellen, erste Entwürfe von Oberfläche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infoterminal verbesserung in der Auswahl von Infoseiten, Logischere Funktionalere Struktur beim crud.    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einstieg in Svelte Frondend Framework. </t>
-  </si>
-  <si>
-    <t>Erstes Crud To Do Liste erstellt.</t>
-  </si>
-  <si>
     <t>UML design für Kivy Projekt Erstellt</t>
   </si>
   <si>
@@ -174,17 +116,80 @@
     <t xml:space="preserve">Infoterminal,Kivy </t>
   </si>
   <si>
-    <t xml:space="preserve">Projektplannung IHK,  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Svelte,Kivy </t>
+  </si>
+  <si>
+    <t>Svelte,Kivy</t>
+  </si>
+  <si>
+    <t>Ferien</t>
+  </si>
+  <si>
+    <t>Svelte, Kivy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poverpoint Presentation Kivy Thema spieleentwicklung </t>
+  </si>
+  <si>
+    <t>Daten durch Auswahl von mehreren Templates mit Verzeigungen verbunden, so dass auch die korrekten Dateien in der Datenbank landen.</t>
+  </si>
+  <si>
+    <t>Infoterminal Projekt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsive Web designe vom Dashboard bearbeitet.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python Klassen, Vererbungen von Methoden behandelt. </t>
+  </si>
+  <si>
+    <t>Statische und nicht statische Methoden.</t>
+  </si>
+  <si>
+    <t>krank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projektplannung IHK, ideen gesammelt für ein neues Projekt. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klassenarbeit Python </t>
+  </si>
+  <si>
+    <t>Klassendiagramm struktur erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infoterminal verbesserung in der Auswahl von Infoseiten, ;Logischere funktionalere Struktur beim crud.    </t>
+  </si>
+  <si>
+    <t>Applikation Einstellungen im Administationspanel; Funktionalität verbessert.</t>
+  </si>
+  <si>
+    <t>Projekt Kivy App erstellen, erste Entwürfe von Oberfläche:; Thema Spieleentwicklung</t>
+  </si>
+  <si>
+    <t>Erstes Crud To Do Liste erstellt;. Einstieg in Dizzle Framework(ORM)</t>
+  </si>
+  <si>
+    <t>Einstieg in Svelte Frondend Framework. ;Fundamental gelernt</t>
+  </si>
+  <si>
+    <t>Dokumentation über Infoterminal und ;IHK Projekt angegangen.</t>
+  </si>
+  <si>
+    <t>Datenbank anbindung mit verschiedenen;Datenbänken hergestellt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infoterminal Update, Daten Backup vom laufenden; Projekt gemacht und wieder hergestellt.; Neues Feature implementiert. </t>
+  </si>
+  <si>
+    <t>Daten durch Auswahl von mehreren Templates mit; Verzeigungen verbunden,so dass auch; die korrekten Dateien in der Datenbank landen.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,6 +222,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -238,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -246,6 +257,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,11 +545,11 @@
   <cols>
     <col min="1" max="2" width="9.109375" style="1"/>
     <col min="3" max="3" width="9.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="61.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="84.5546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.5546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="27.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="102.21875" style="1" customWidth="1"/>
     <col min="9" max="9" width="9.109375" style="1"/>
     <col min="10" max="10" width="27.6640625" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.109375" style="1"/>
@@ -546,10 +560,10 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -592,28 +606,28 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>38</v>
+        <v>16</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
@@ -621,254 +635,169 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>117</v>
+      </c>
+      <c r="B5" s="1">
+        <v>49</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="35.4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>123</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="2"/>
       <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B6" s="1">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="C6" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>2025</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="E6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H6" s="2"/>
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B7" s="1">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>48</v>
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H7" s="2"/>
       <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B8" s="1">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>127</v>
-      </c>
-      <c r="B9" s="1">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>128</v>
-      </c>
-      <c r="B10" s="1">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>129</v>
-      </c>
-      <c r="B11" s="1">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B12" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1">
         <v>2026</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
@@ -876,57 +805,57 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B13" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C13" s="1">
         <v>2026</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="35.4" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B14" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1">
         <v>2026</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
@@ -934,28 +863,28 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B15" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1">
         <v>2026</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>8</v>
@@ -963,28 +892,28 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B16" s="1">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1">
         <v>2026</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>8</v>
@@ -992,28 +921,28 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B17" s="1">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1">
         <v>2026</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
@@ -1021,28 +950,28 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B18" s="1">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1">
         <v>2026</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>8</v>
@@ -1050,28 +979,28 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B19" s="1">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1">
         <v>2026</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>8</v>
@@ -1079,175 +1008,30 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B20" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C20" s="1">
         <v>2026</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>139</v>
-      </c>
-      <c r="B21" s="1">
-        <v>19</v>
-      </c>
-      <c r="C21" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>140</v>
-      </c>
-      <c r="B22" s="1">
-        <v>20</v>
-      </c>
-      <c r="C22" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
-        <v>141</v>
-      </c>
-      <c r="B23" s="1">
-        <v>21</v>
-      </c>
-      <c r="C23" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
-        <v>142</v>
-      </c>
-      <c r="B24" s="1">
-        <v>22</v>
-      </c>
-      <c r="C24" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
-        <v>143</v>
-      </c>
-      <c r="B25" s="1">
-        <v>23</v>
-      </c>
-      <c r="C25" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BerichteGenerierenJSt_2026/data.xlsx
+++ b/BerichteGenerierenJSt_2026/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8c5f5e60cbc7cb48/BerichteGenerierenJSt/BerichteGenerierenJSt_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{615000B2-D201-42A9-9881-0A8EEB2B7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C53D807A-9F61-4C35-9986-51BB02D62CD8}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="13_ncr:1_{615000B2-D201-42A9-9881-0A8EEB2B7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20D2BDB6-D484-4208-9ACC-8B3A0C006F0C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="49">
   <si>
     <t>Bericht</t>
   </si>
@@ -95,9 +95,6 @@
     <t xml:space="preserve">Urlaub </t>
   </si>
   <si>
-    <t xml:space="preserve">Ferien </t>
-  </si>
-  <si>
     <t xml:space="preserve">Einstieg in Kivy Übungsaufgaben. </t>
   </si>
   <si>
@@ -158,9 +155,6 @@
     <t>Klassendiagramm struktur erstellen</t>
   </si>
   <si>
-    <t xml:space="preserve">Infoterminal verbesserung in der Auswahl von Infoseiten, ;Logischere funktionalere Struktur beim crud.    </t>
-  </si>
-  <si>
     <t>Applikation Einstellungen im Administationspanel; Funktionalität verbessert.</t>
   </si>
   <si>
@@ -182,7 +176,13 @@
     <t xml:space="preserve">Infoterminal Update, Daten Backup vom laufenden; Projekt gemacht und wieder hergestellt.; Neues Feature implementiert. </t>
   </si>
   <si>
-    <t>Daten durch Auswahl von mehreren Templates mit; Verzeigungen verbunden,so dass auch; die korrekten Dateien in der Datenbank landen.</t>
+    <t xml:space="preserve">Infoterminal verbesserung in der Auswahl von Infoseiten,;Logischere funktionalere Struktur beim crud.    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Daten durch Auswahl von mehreren Templates mit; Verzeigungen verbunden,;so dass auch; die korrekten Dateien in der Datenbank landen.</t>
   </si>
 </sst>
 </file>
@@ -275,6 +275,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -615,19 +619,19 @@
         <v>2025</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
@@ -644,19 +648,19 @@
         <v>2025</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
@@ -673,19 +677,19 @@
         <v>2025</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
@@ -702,18 +706,20 @@
         <v>2025</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
@@ -735,12 +741,14 @@
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
@@ -761,14 +769,12 @@
       <c r="E8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
@@ -790,14 +796,12 @@
       <c r="E12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
@@ -819,14 +823,12 @@
       <c r="E13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>8</v>
@@ -843,19 +845,19 @@
         <v>2026</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
@@ -872,19 +874,19 @@
         <v>2026</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>8</v>
@@ -901,19 +903,19 @@
         <v>2026</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>8</v>
@@ -930,19 +932,19 @@
         <v>2026</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
@@ -959,19 +961,19 @@
         <v>2026</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>8</v>
@@ -988,19 +990,19 @@
         <v>2026</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>8</v>
@@ -1017,19 +1019,19 @@
         <v>2026</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>8</v>

--- a/BerichteGenerierenJSt_2026/data.xlsx
+++ b/BerichteGenerierenJSt_2026/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8c5f5e60cbc7cb48/BerichteGenerierenJSt/BerichteGenerierenJSt_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="13_ncr:1_{615000B2-D201-42A9-9881-0A8EEB2B7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20D2BDB6-D484-4208-9ACC-8B3A0C006F0C}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{615000B2-D201-42A9-9881-0A8EEB2B7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1837F47D-9303-4C9B-9089-8D9E3C9305CC}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="3948" windowWidth="17280" windowHeight="8844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -128,9 +128,6 @@
     <t xml:space="preserve">Poverpoint Presentation Kivy Thema spieleentwicklung </t>
   </si>
   <si>
-    <t>Daten durch Auswahl von mehreren Templates mit Verzeigungen verbunden, so dass auch die korrekten Dateien in der Datenbank landen.</t>
-  </si>
-  <si>
     <t>Infoterminal Projekt</t>
   </si>
   <si>
@@ -183,6 +180,9 @@
   </si>
   <si>
     <t>Daten durch Auswahl von mehreren Templates mit; Verzeigungen verbunden,;so dass auch; die korrekten Dateien in der Datenbank landen.</t>
+  </si>
+  <si>
+    <t>Daten durch Auswahl von mehreren Templates mit Verzeigungen verbunden,; so dass auch die korrekten Dateien in der Datenbank landen.</t>
   </si>
 </sst>
 </file>
@@ -619,19 +619,19 @@
         <v>2025</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
@@ -648,19 +648,19 @@
         <v>2025</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
@@ -677,19 +677,19 @@
         <v>2025</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
@@ -706,19 +706,19 @@
         <v>2025</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
@@ -735,19 +735,19 @@
         <v>2025</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
@@ -845,7 +845,7 @@
         <v>2026</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>13</v>
@@ -857,7 +857,7 @@
         <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
@@ -874,7 +874,7 @@
         <v>2026</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>13</v>
@@ -903,7 +903,7 @@
         <v>2026</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>13</v>
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>13</v>
@@ -944,7 +944,7 @@
         <v>16</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
@@ -961,7 +961,7 @@
         <v>2026</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>13</v>
@@ -990,7 +990,7 @@
         <v>2026</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>13</v>
@@ -1031,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>8</v>

--- a/BerichteGenerierenJSt_2026/data.xlsx
+++ b/BerichteGenerierenJSt_2026/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8c5f5e60cbc7cb48/BerichteGenerierenJSt/BerichteGenerierenJSt_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{615000B2-D201-42A9-9881-0A8EEB2B7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1837F47D-9303-4C9B-9089-8D9E3C9305CC}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="13_ncr:1_{615000B2-D201-42A9-9881-0A8EEB2B7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{966AA77C-890C-43A0-84D6-241BC8EA03D7}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="3948" windowWidth="17280" windowHeight="8844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="50">
   <si>
     <t>Bericht</t>
   </si>
@@ -152,37 +152,40 @@
     <t>Klassendiagramm struktur erstellen</t>
   </si>
   <si>
-    <t>Applikation Einstellungen im Administationspanel; Funktionalität verbessert.</t>
-  </si>
-  <si>
-    <t>Projekt Kivy App erstellen, erste Entwürfe von Oberfläche:; Thema Spieleentwicklung</t>
-  </si>
-  <si>
-    <t>Erstes Crud To Do Liste erstellt;. Einstieg in Dizzle Framework(ORM)</t>
-  </si>
-  <si>
-    <t>Einstieg in Svelte Frondend Framework. ;Fundamental gelernt</t>
-  </si>
-  <si>
-    <t>Dokumentation über Infoterminal und ;IHK Projekt angegangen.</t>
-  </si>
-  <si>
-    <t>Datenbank anbindung mit verschiedenen;Datenbänken hergestellt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infoterminal Update, Daten Backup vom laufenden; Projekt gemacht und wieder hergestellt.; Neues Feature implementiert. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infoterminal verbesserung in der Auswahl von Infoseiten,;Logischere funktionalere Struktur beim crud.    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Daten durch Auswahl von mehreren Templates mit; Verzeigungen verbunden,;so dass auch; die korrekten Dateien in der Datenbank landen.</t>
-  </si>
-  <si>
-    <t>Daten durch Auswahl von mehreren Templates mit Verzeigungen verbunden,; so dass auch die korrekten Dateien in der Datenbank landen.</t>
+    <t>Daten durch Auswahl von mehreren Templates mit Verzeigungen verbunden,so dass auch die korrekten Dateien in der Datenbank landen.</t>
+  </si>
+  <si>
+    <t>Daten durch Auswahl von mehreren Templates mit Verzeigungen verbunden, so dass auch die korrekten Dateien in der Datenbank landen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infoterminal Update, Daten Backup vom laufenden Projekt gemacht und wieder hergestellt. Neues Feature implementiert. </t>
+  </si>
+  <si>
+    <t>Applikation Einstellungen im Administationspanel Funktionalität verbessert.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infoterminal verbesserung in der Auswahl von Infoseiten, Logischere funktionalere Struktur beim crud.    </t>
+  </si>
+  <si>
+    <t>Dokumentation über Infoterminal und IHK Projekt angegangen.</t>
+  </si>
+  <si>
+    <t>Einstieg in Svelte Frondend Framework. Fundamental gelernt</t>
+  </si>
+  <si>
+    <t>Erstes Crud To Do Liste erstellt. Einstieg in Dizzle Framework(ORM)</t>
+  </si>
+  <si>
+    <t>Datenbank anbindung mit verschiedenen Datenbänken hergestellt.</t>
+  </si>
+  <si>
+    <t>Projekt Kivy App erstellen, erste Entwürfe von Oberfläche: Thema Spieleentwicklung</t>
+  </si>
+  <si>
+    <t>Lambda, map Funktionen behandelt.</t>
+  </si>
+  <si>
+    <t>Ablaufdiagramm erstellt.</t>
   </si>
 </sst>
 </file>
@@ -619,7 +622,7 @@
         <v>2025</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>13</v>
@@ -677,7 +680,7 @@
         <v>2025</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>13</v>
@@ -706,7 +709,7 @@
         <v>2025</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>13</v>
@@ -718,7 +721,7 @@
         <v>16</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
@@ -735,7 +738,7 @@
         <v>2025</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>13</v>
@@ -747,7 +750,7 @@
         <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
@@ -845,7 +848,7 @@
         <v>2026</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>13</v>
@@ -903,7 +906,7 @@
         <v>2026</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>13</v>
@@ -932,7 +935,7 @@
         <v>2026</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>13</v>
@@ -944,7 +947,7 @@
         <v>16</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
@@ -961,7 +964,7 @@
         <v>2026</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>13</v>
@@ -990,7 +993,7 @@
         <v>2026</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>13</v>

--- a/BerichteGenerierenJSt_2026/data.xlsx
+++ b/BerichteGenerierenJSt_2026/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8c5f5e60cbc7cb48/BerichteGenerierenJSt/BerichteGenerierenJSt_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="13_ncr:1_{615000B2-D201-42A9-9881-0A8EEB2B7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{966AA77C-890C-43A0-84D6-241BC8EA03D7}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="13_ncr:1_{615000B2-D201-42A9-9881-0A8EEB2B7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DF7E37E-62D5-4974-AC09-8157DBCDC292}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="51">
   <si>
     <t>Bericht</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>Ablaufdiagramm erstellt.</t>
+  </si>
+  <si>
+    <t>Infoterminal; Projekt</t>
   </si>
 </sst>
 </file>
@@ -686,7 +689,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>16</v>
@@ -767,7 +770,7 @@
         <v>2025</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>13</v>
